--- a/src/test/resources/advanced_filters_excel_sheets/filters_expected_ctc.xlsx
+++ b/src/test/resources/advanced_filters_excel_sheets/filters_expected_ctc.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\workspace-spring-tools-for-eclipse-4.31.0.RELEASE\SSWebsite\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\Eticaa Project Automation\Eticaa-Automation\src\test\resources\advanced_filters_excel_sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0966458-7913-4631-A06B-9BACBCE9B66F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EFAB30F-AFC7-4198-BCB6-4A3234E769DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ExperienceRanges" sheetId="1" r:id="rId1"/>
+    <sheet name="ExpectedCTCFilters" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -381,9 +381,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -391,7 +391,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2</v>
       </c>
@@ -399,7 +399,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>3</v>
       </c>
@@ -407,7 +407,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>4</v>
       </c>
@@ -415,7 +415,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>5</v>
       </c>
@@ -423,7 +423,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>6</v>
       </c>
@@ -431,7 +431,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>8</v>
       </c>
@@ -439,7 +439,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>10</v>
       </c>
@@ -447,7 +447,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>12</v>
       </c>
@@ -455,7 +455,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>15</v>
       </c>
@@ -463,7 +463,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>20</v>
       </c>
@@ -471,7 +471,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>0</v>
       </c>
@@ -479,7 +479,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -487,7 +487,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>5</v>
       </c>
@@ -495,7 +495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>0</v>
       </c>
@@ -503,7 +503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>0</v>
       </c>
@@ -511,7 +511,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>0</v>
       </c>
@@ -519,7 +519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>25</v>
       </c>
@@ -527,7 +527,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>40</v>
       </c>
@@ -535,7 +535,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>60</v>
       </c>
@@ -543,7 +543,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>100</v>
       </c>
